--- a/docs/feature-list.xlsx
+++ b/docs/feature-list.xlsx
@@ -1066,21 +1066,23 @@
           <t>AI 会话</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>机构 Token 超限拦截</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>（1）〔演示〕由落地页演示开关触发；生产由机构实际 Token 用量判定
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>0824周一更新
+（1）〔演示〕由落地页演示开关触发；生产由机构实际 Token 用量判定
 （2）超限时会话顶部常驻珊瑚红提示条「当前机构 Token 已达上限，请联系客服」
-（3）发送消息、语音输入、点实时电话入口均被拦截；被拦时让顶部提示条放大抖动+跳亮提醒，不再额外弹 toast</t>
+（3）发送消息、语音输入、点实时电话入口均被拦截；被拦时让顶部提示条放大抖动+跳亮提醒，不再额外弹 toast
+（4）「0824 新增」机构停用拦截共用本提示条与拦截逻辑（停用优先于 Token 超限展示）：提示条文案「机构服务已暂停，暂时无法使用问答服务；如有疑问请到「我的 - 联系客服」」；仅拦问答服务（提问/语音/实时电话），「我的」层保持可达（我的/订单/联系客服）——停用通知短信把用户指向「我的-联系客服」，账户层不能拦，否则短信指引与产品行为自相矛盾。〔演示〕落地页演示开关「机构正常/机构已停用」触发</t>
         </is>
       </c>
     </row>
@@ -1126,22 +1128,24 @@
           <t>付费墙与权益</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>多模态付费墙</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>（1）受限媒体触发，按资源所属权益池动态呈现按钮（不再固定两按钮）：
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>0824周一更新
+（1）受限媒体触发，按资源所属权益池动态呈现按钮（不再固定两按钮）：
 （2）会员资源：标题「{资源名} · 会员内容」+ 单按钮「开通会员 · 畅享全部会员内容」（进会员页）
 （3）永享资源：标题「{资源名} · 永享内容」+ 单按钮「¥X 永久解锁此内容」（经手机号绑定门槛后进微信支付收银台），文案点明「永享内容单独购买，无需开通会员」
-（4）金额取该资源的永享价（非硬编码）；付费墙去除左侧锁图标，标题/描述/按钮整体居中</t>
+（4）金额取该资源的永享价（非硬编码）；付费墙去除左侧锁图标，标题/描述/按钮整体居中
+（5）「0824 新增」永享路径协议勾选（会话内付费墙与 lightbox 内付费墙同一套）：两条业务路径各取一次明示同意——已勾会员协议不豁免永享、反之亦然（明示同意须针对特定交易，举证时同意时间直接对应具体业务）。① 首次从永享路径购买（未同意过）：按钮上方出现勾选行「已阅读并同意《AI 会员服务与永享服务协议》」，默认不勾、须手动勾选，未勾时按钮降透明度、点击 toast「请先阅读并同意《AI 会员服务与永享服务协议》」拦截；② 已同意过：勾选行替换为灰字「购买即视为同意《AI 会员服务与永享服务协议》」（保留知情、去掉动作），此后所有永享购买均免勾；③ 同意时点＝勾选后点击购买按钮进收银台即记录（同意的对象是协议文本，不依赖支付结果）；协议名可点进正文页。同意记录粒度＝用户 × 协议 × 版本 × 业务路径 × 时间（附首单号快照）；协议升版重置本批不涉及。〔演示〕落地页开关「永享协议未同意/已同意」可反复演示两态</t>
         </is>
       </c>
     </row>
@@ -1197,17 +1201,18 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>0814周五更新
+          <t>0824周一更新
 （1）0717 二批 #9：两档改为「购买方式即续费语义」，消除「按月自动续费」歧义——① 连续包月（默认选中，角标「首月特惠」）：首月 ¥9.9、次月起 ¥19.9/月 自动续费，卡内说明「自动续费，可随时退订」② 单月（¥19.9 / 1 个月）：一次性购买，卡内说明「到期自动失效，不自动续费不扣款」；选中即表达是否自动续费，不再靠一个含糊的全局勾选
 （2）协议、按钮与底部说明随所选方式联动：连续包月→勾选《自动续费协议》+ 按钮「¥9.9 开通连续包月」+ 底部说明「次月起 ¥19.9/月 自动扣费 · 支持随时退订，到期赠 72 小时会员缓冲使用期」；单月→协议行换成《会员服务协议》（无自动续费协议）+ 按钮「¥19.9 购买单月会员」+ 底部说明「到期自动失效，不会自动扣费」；缓冲期不计入已付费会员时长
 （3）「立即开通」前校验手机号绑定（未绑先引导绑定再继续），通过后按所选方式进微信支付收银台
 （4）「0718 修订」开通会员页按「先权益、再套餐、后协议」重构交互：① 标题下新增三枚权益速览 chip（受限内容全解锁 / 图音视频精讲 / 电话问答·VIP 优先）；② 套餐卡信息层级重排——卡名 + 续费语义 pill（连续包月＝「自动续费 · 可随时取消」琥珀标；单月＝「一次性购买 · 不自动续费」灰标）+ 一行说明 + 右侧大价签；选中态改左侧对勾圆点（琥珀填充）+ 琥珀描边淡底，「首月特惠」角标改琥珀渐变；③ 协议勾选改为真实可点交互（未勾选点按钮 toast 引导先同意协议），连续包月需同意《会员服务协议》《自动续费协议》两份，单月仅《会员服务协议》；④ 按钮与底部说明随所选方式联动（语义与 0717 二批 #9 不变：连续包月＝首月 ¥9.9、次月起 ¥19.9/月 自动续费可退订；单月＝¥19.9 一次性、到期自动失效）
 （5）「0718 修订」删除开通按钮下方的补充说明文案（原「次月起 ¥19.9/月 自动扣费 · 支持随时退订，到期赠 72 小时会员缓冲使用期」/「一次性购买 · 到期自动失效，不会自动扣费」），续费规则由套餐卡内的续费语义 pill 与说明承载，不再页底重复
 （6）「0719 修订」协议勾选框改为**默认未勾选**，须用户主动勾选后方可开通（原默认已勾选）——连续包月场景含《自动续费协议》，默认代勾在国内合规口径下通常不被接受；同时与登录落地页「协议默认未勾选」的口径保持一致。未勾选时开通按钮呈置灰视觉，点击 toast「请先阅读并同意相关协议」并阻断，不进收银台
-（7）「0812 新增」会员月度周期按「对日周期」计算：自开通当日起顺延至次月同日；若次月无对应日期，则顺延至当月最后一日，后续续费持续按该日期执行。示例：1 月 31 日开通，2 月无 31 日，当期有效期至 2 月 28 日，后续每月 28 日自动续费。扣费日＝到期日前 1 天（商户预约扣费节奏，详见 PRD 4.4.5）
+（7）「0812 新增」会员月度周期按「对日周期」计算：自开通当日起顺延至次月同日；若次月无对应日期，则顺延至当月最后一日，后续续费持续按该日期执行。示例：1 月 31 日开通，2 月无 31 日，当期有效期至 2 月 28 日，后续每月 28 日自动续费。扣费日＝到期日前 1 天（商户预约扣费节奏，详见 PRD 4.4.5）【0824-3 收口：扣费日改为到期日当天，本条前述「前 1 天」作废，理由与定版见 3.4 会员中心 0824-3 条】
 （8）「0814-2 新增」套餐卡与协议之间新增「缓冲期安心提示」常驻一行：「会员到期附赠 72 小时 缓冲期，权益持续可用，缓冲期不计会员时长。」——原 72 小时缓冲期只在《会员服务协议》正文与到期后的界面里出现，用户在付费决策时看不到；该承诺是降低「怕买了到期就断」焦虑的兜底项，须在付费前完成告知。视觉上刻意不并入顶部权益速览 chip：缓冲期是兜底承诺不是卖点，用中性灰底细条 + 玉绿盾形图标，不与琥珀套餐卡抢注意力
 （9）「0814-2 修订」连续包月卡内说明中的「次月起 ¥19.9/月」加粗加深（原与整行同字重）：首月 ¥9.9 是拉新钩子，次月价才是用户长期实际支付的金额，不应被淹没在一行小字里——付费前把真实长期成本讲清楚，减少后续因「不知道会涨价」产生的退订与投诉
-（10）「0814-2 修订」单月会员卡说明由「¥19.9 / 1 个月，到期自动失效不扣款，适合先体验一个月」改为「¥19.9 / 1 个月，到期不扣款、不自动续期，适合先体验一个月」——原「到期自动失效」与「到期赠 72 小时缓冲」直接矛盾。口径定版：缓冲期的目的是防止服务突然中断伤害体验，与是否开通自动续费无关，连续包月与单月两档一视同仁均赠 72 小时缓冲；「不扣款」表达的是计费语义，与权益是否立即终止解耦</t>
+（10）「0814-2 修订」单月会员卡说明由「¥19.9 / 1 个月，到期自动失效不扣款，适合先体验一个月」改为「¥19.9 / 1 个月，到期不扣款、不自动续期，适合先体验一个月」——原「到期自动失效」与「到期赠 72 小时缓冲」直接矛盾。口径定版：缓冲期的目的是防止服务突然中断伤害体验，与是否开通自动续费无关，连续包月与单月两档一视同仁均赠 72 小时缓冲；「不扣款」表达的是计费语义，与权益是否立即终止解耦
+（11）「0824 修订」协议定版为合体《AI 会员服务与永享服务协议》（会员订阅与永享买断共用一份文本，替换原《会员服务协议》命名）：协议行改「已阅读并同意《AI 会员服务与永享服务协议》」+ 连续包月另加《自动续费协议》，两个协议名由死链改为真实跳转协议正文页（/agreement/member、/agreement/autopay）。勾选口径定版：用户主动发起的每次购买都勾选——含断档过期后重开、宽限期「立即续费」（都走开通会员页，都是新签约/新代扣授权）；连续包月存续期间的按月自动扣款是履约不是新约、不勾选（也无交互场景）。已在永享路径同意过合体协议不豁免会员路径勾选（两条路径各取一次明示同意）</t>
         </is>
       </c>
     </row>
@@ -1234,17 +1239,19 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>0814周五更新
+          <t>0824周一更新
 （1）会员卡：会员标识 + 有效期 + 续费状态（自动续费 / 到期不再续费）
 （2）「免费 vs 会员」权益对比表（逐项 ✅/✗）：基础文字知识问答、图音视频深度知识精讲、VIP 极速优先通道、实时电话即时问答、永享名家典藏知识（永享标注为「单独购买」）
 （3）底部说明「自动续费将于扣费前 5 天短信提醒，可随时取消」
-（4）「0812 修订」自动续费提醒时点定版为「扣费前 5 天」（原「到期前 3 天」作废；扣费日＝到期日前 1 天）。续费提醒短信模版（签名固定【科技文献出版社】，非动态机构名）——标准版：「【科技文献出版社】您订购的AI问书会员将于${到期日}到期，${扣费日}我们将通过微信自动续费${金额}元。如需退订，请前往微信"我的-服务-钱包-支付设置-自动续费/免密支付"管理。」降价版（会员价下调时合并降价告知，一条短信一并通知）：「【科技文献出版社】您订购的AI问书会员将于${到期日}到期。会员价已由${原价}元调整为${新价}元，${扣费日}我们将通过微信按新价格${新价}元自动续费。如需退订，请前往微信"我的-服务-钱包-支付设置-自动续费/免密支付"管理。」
+（4）「0812 修订」自动续费提醒时点定版为「扣费前 5 天」（原「到期前 3 天」作废；扣费日＝到期日前 1 天）。续费提醒短信模版（签名固定【科技文献出版社】，非动态机构名）——标准版：「【科技文献出版社】您订购的AI问书会员将于${到期日}到期，${扣费日}我们将通过微信自动续费${金额}元。如需退订，请前往微信"我的-服务-钱包-支付设置-自动续费/免密支付"管理。」降价版（会员价下调时合并降价告知，一条短信一并通知）：「【科技文献出版社】您订购的AI问书会员将于${到期日}到期。会员价已由${原价}元调整为${新价}元，${扣费日}我们将通过微信按新价格${新价}元自动续费。如需退订，请前往微信"我的-服务-钱包-支付设置-自动续费/免密支付"管理。」【0824-3 收口：本条「扣费日＝到期日前 1 天」作废、模版中两个日期合并，扣费日改为到期日当天，定版模版见本功能点 0824-3 条】
 （5）「0814-2 新增」会员中心改为按会员四态渲染（原页面只有「有效会员」一种形态，且有效期硬编码，宽限期 / 已过期 / 未开通用户进入均看到一张有效会员卡——属错误展示，本次一并修正）。四态卡面：① 有效会员＝靛紫卡，「有效期至 {日期}」+ 续费状态「按月自动续费 / 到期不再续费」+ 按钮「取消自动续费 / 自动续费」；② 宽限期＝琥珀卡（详见下条）；③ 会员已过期＝灰卡 + 角标「已失效」+「会员已到期 {日期}」+「权益已暂停」+ 按钮「重新开通会员」（无底部说明）；④ 未开通＝灰卡 + 角标「未开通」+「尚未开通 / —」+「开通后即刻生效」+ 按钮「开通会员」+ 底部说明「开通后受限内容即刻解锁；到期额外赠送 72 小时缓冲使用期」。「免费 vs 会员」权益对比表四态均保留（对已流失用户即价值召回）
 （6）「0814-2 新增」宽限期（到期后 72 小时缓冲使用期）C 端展示定版。信息优先级按「用户此刻真正关心什么」排序：① 我还能用吗 → ② 还剩多久 → ③ 我该做什么。卡面：保持会员卡形态不降级为空态（缓冲期内权益仍生效，降级成空态等于告诉用户他不是会员），仅换琥珀色调；「会员」字样右侧加角标「已到期」；主信息位 lab 改「权益还可使用」、大字改倒计时「剩 {N} 小时」（琥珀强调色），到期日退为次要信息「已于 {日期} 到期」；卡内不放任何机制说明（详见下条）；主按钮唯一动作「立即续费 · 恢复会员」→ 开通会员页；无底部说明
 （7）「0814-3 修复」会员卡显式左对齐（原继承页面 text-align:center）。原先看不出问题，是因为卡内每个盒子的宽度恰好等于自身文字宽度，居中没有可见效果；本批给宽限期加了「已到期」角标、并把倒计时字号调大后，mc-brand / mc-valid 被撑宽，同列较窄的「AI 问书」「权益还可使用」开始居中偏移，表现为左边空一块、且只在部分会员状态下出现。修法不是逐个状态调间距，而是给卡片补 text-align:left——四态一致，且后续再加任何角标或改字号都不会复发
 （8）「0814-3 修订」宽限期卡面「不变脸」＋机制说明改按需展开（推翻 0814-2 初稿的「整卡转琥珀 + 卡内常驻说明段落」）。① 卡底仍用有效会员的靛紫，不整卡转暖——宽限期内权益一样都没少，整卡变色等于暗示身份降级，不准确；且暖卡配靛紫知识球必然撞色。警示色只给真正需要行动的那一个元素＝倒计时（外加「已到期」琥珀角标），「会员」二字保持品牌渐变不染警示色。由此形成三档卡面语言：有效＝靛紫 / 宽限期＝靛紫＋琥珀警示元素 / 已过期＝灰，宽限期在视觉上正好落在两者之间，与其语义一致。② 卡内那段「会员到期附赠 72 小时缓冲期……」整段删除——卡片是身份凭证不是条款栏，且卡上「已到期」+「权益还可使用 剩 N 小时」两个标签已把「到期了 / 还能用 / 还剩多久」说完，该段是同一件事说第二遍。③ 机制说明改为卡外一行可点链接「为什么到期了还能用？」→ 半屏 sheet「关于到期缓冲期」，主按钮「知道了」。三段文案定版：「会员到期享 72 小时缓冲期，全部会员权益正常可用。」「缓冲时长不计会员有效期，缓冲期续费，新时长从缴费当日起算。」「缓冲期满权益暂停，续费后即可立即恢复使用。」链接文案直接用用户的原始疑问，不出现「缓冲期」这一机制名词（与本批 C 端不出现「宽限期」的原则一致）
 （9）「0814-2 口径」缓冲期内续费的有效期起算时点＝实际缴费时刻，不是上一期的到期日。沿用既有顺延规则「会员时长自 max（当前时间, 当前已付费会员到期时间）起顺延累加」——缓冲期内当前时间已晚于到期时间，故取当前时间，用户不会为缓冲期这段时间二次付费。（本条为对既有规则的显式重申：0814-2 初稿曾在宽限期底部写「续费后有效期自 {到期日} 顺延」，与该规则冲突，已随底部说明一并删除）
-（10）「0814-2 口径」宽限期展示的三条定版原则：① C 端不出现「宽限期」这一状态名词——运营四态语义（有效会员 / 宽限期（待续费）/ 会员已过期 / 未开通会员）只在两个后台使用；C 端不让用户先理解一个状态名再自行推断后果，直接讲他能感知的事实「还能用多久」。② 倒计时全程用小时制，向上取整，剩余 ≤1 小时显示「不足 1 小时」，出窗口显示「缓冲期已结束」——72 小时尺度下换算成「2 天 23 小时」会被读成「还早」，反而削弱紧迫感。③ 用琥珀不用赤陶——赤陶＝已失效，琥珀＝还能用但需行动，与两个后台四态标签色（玉绿/琥珀/赤陶/灰）同源。宽限期不区分成因（自动续费扣款失败 / 未开自动续费自然到期）展示同一套文案，CTA 统一为「立即续费」</t>
+（10）「0814-2 口径」宽限期展示的三条定版原则：① C 端不出现「宽限期」这一状态名词——运营四态语义（有效会员 / 宽限期（待续费）/ 会员已过期 / 未开通会员）只在两个后台使用；C 端不让用户先理解一个状态名再自行推断后果，直接讲他能感知的事实「还能用多久」。② 倒计时全程用小时制，向上取整，剩余 ≤1 小时显示「不足 1 小时」，出窗口显示「缓冲期已结束」——72 小时尺度下换算成「2 天 23 小时」会被读成「还早」，反而削弱紧迫感。③ 用琥珀不用赤陶——赤陶＝已失效，琥珀＝还能用但需行动，与两个后台四态标签色（玉绿/琥珀/赤陶/灰）同源。宽限期不区分成因（自动续费扣款失败 / 未开自动续费自然到期）展示同一套文案，CTA 统一为「立即续费」
+（11）「0824 新增」自动续费扣款失败重试与解约定版（后端规则，无 C 端界面变更；详见 PRD 4.4.5 ④-2）。① 重试节奏＝自扣费日起连续 3 天、每日一次：T0（扣费日＝到期日当天，0824-3 修订见下条）/ T+1（到期后第 1 天）/ T+2（到期后第 2 天），共 3 次，三次全部落在 72 小时缓冲期内——微信自动续费模板同一用户同一签约协议每日仅可扣款一次，重试只能跨天分布；且失败主因余额不足的自愈周期以「天」计，跨天重试同时匹配平台约束与失败成因。② T+2 仍失败即停止重试；缓冲期剩余约 24 小时纯作用户手动续费的挽留窗口；缓冲期结束（到期后 72 小时）仍未续费 → 转「会员已过期」+ 主动解除微信代扣签约 + 发解约短信——三件事在缓冲期结束时点同时发生，保证解约短信「权益已暂停」的表述与事实一致；本期不补扣、下个周期不再发起扣款、不存在跨周期或永久重试（与微信预约扣费「可扣费期结束系统自动解约」的平台机制一致）。③ 防双扣＝同一订阅周期只允许成功一笔；重试期间用户手动续费成功即取消本期剩余重试任务。④ 重试成功（T+1/T+2）的新周期自实际扣款成功时刻起算——与「缓冲期内续费自缴费时刻起算」同一条顺延规则，零例外。⑤ 「0824-3 修订」每次扣款失败均发短信（T0/T+1/T+2 最多三条，统一模版、以 ${剩余小时} 变量适配）：「【科技文献出版社】您在${机构名}的AI问书会员自动续费未成功，会员权益还可使用${剩余小时}小时，请及时续费以免影响使用。」剩余小时取 72 / 48 / 24（T0 失败时权益恰进入缓冲期，三次均在 72 小时内，文案永远为真）；缓冲期结束发解约短信「【科技文献出版社】您在${机构名}的AI问书会员因连续扣款失败，已停止自动续费，会员权益已暂停。如需继续使用，可随时在AI问书重新开通。」（C 端不出现「解约」字眼——用户需要知道的是「不会再扣钱」，签约从微信列表消失是符合预期的结果；失败版与解约版均带 ${机构名}——用户可能在多家机构开过会员，资金相关短信必须可对账到具体服务）。⑥ 本条与机构停用共同确立统一原则：凡决定不再扣款一律主动解约，「签约存在＝未来会扣款」在系统内恒成立，不留僵尸签约
+（12）「0824-3 新增」扣费日定版＝到期日当天（推翻 0812「到期日前 1 天」，0812 各处旧表述以本条为准作废）。行业提前 1 天扣（爱奇艺 / 腾讯视频均为到期前 24h）的唯一功能性理由是「防扣款失败断服」，而本产品的 72 小时缓冲期已结构性替代该职责——提前扣的收益消失，只剩成本：① 为尚未开始的周期提前收钱是自动续费投诉的经典触发点；② 破坏对日周期语义（0812 自己的示例「此后每月 28 日自动续费」中 28 日即到期日，与「前 1 天扣」自相矛盾），改当天扣后「每月 X 号扣费」零解释成本。连带修订两处：续费提醒短信仍为扣费前 5 天（＝到期前 5 天），模版中「${到期日}到期，${扣费日}扣费」两个日期合并——标准版：「【科技文献出版社】您订购的AI问书会员将于${到期日}到期，到期当天我们将通过微信自动续费${金额}元。如需退订，请前往微信"我的-服务-钱包-支付设置-自动续费/免密支付"管理。」降价版同规则合并日期。新增扣费成功短信（首扣 / 重试成功均发）：「【科技文献出版社】您在${机构名}的AI问书会员已续费成功，本次扣费${金额}元，会员有效期至${到期日}。如需退订，请前往微信"我的-服务-钱包-支付设置-自动续费/免密支付"管理。」</t>
         </is>
       </c>
     </row>
@@ -1734,20 +1741,22 @@
           <t>协议与辅助页</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>用户协议 / 隐私政策</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>（1）两个独立入口并列，纯文本/Markdown 渲染
-（2）底部展示更新日期</t>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>用户协议 / 隐私政策 / 会员与永享协议 / 自动续费协议</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>0824周一更新
+（1）独立入口并列，纯文本/Markdown 渲染
+（2）底部展示更新日期
+（3）「0824 新增」协议正文由两篇扩为四篇（路由 /agreement/:type）：新增《AI 会员服务与永享服务协议》（合体文本：会员两档与对日周期 / 72h 缓冲使用期 / 自动续费引用 / 扣费失败与服务终止 / 永享买断 / 机构服务变动 / 版权限制）与《自动续费协议》（委托代扣授权 / 扣费日与前 5 天提醒 / 就低不就高价格 / 分日重试与期满解约 / 退订）。其中服务终止条款定版：「重试期满仍未扣费成功的，本服务自动终止，您的会员权益自当前周期届满之日起终止；我们将额外为您提供 72 小时缓冲使用期，缓冲期内权益正常可用、且不计入会员时长。您可随时重新开通。」——原措辞「自当前周期届满之日起终止」与 72h 缓冲期矛盾，本次让文本追上产品（协议是权利下限，产品更宽松不违约，但文本与事实须一致）；该条同时构成扣款失败主动解约的约定基础（有约定 + 有告知 + 既有权益不受损）。⚠️ 上线前条款措辞须法务过目</t>
         </is>
       </c>
     </row>
@@ -1818,20 +1827,21 @@
           <t>协议与辅助页</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>原型清单 / 演示环境开关</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>（1）〔评审〕原型清单：三端站点地图，列全站页面便于评审跳转，脱手机框全宽渲染
-（2）〔演示〕落地页演示环境开关：微信内/浏览器、Token 正常/超限，仅原型演示用、标注非上线功能</t>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>0824周一更新
+（1）〔评审〕原型清单：三端站点地图，列全站页面便于评审跳转，脱手机框全宽渲染
+（2）〔演示〕落地页演示环境开关：微信内/浏览器、Token 正常/超限、会员四态、机构正常/已停用（0824）、永享协议未同意/已同意（0824），仅原型演示用、标注非上线功能</t>
         </is>
       </c>
     </row>
@@ -3339,22 +3349,24 @@
           <t>机构管理</t>
         </is>
       </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>机构列表</t>
         </is>
       </c>
-      <c r="D92" s="3" t="inlineStr">
+      <c r="D92" s="4" t="inlineStr">
         <is>
           <t>停用 / 恢复</t>
         </is>
       </c>
-      <c r="E92" s="6" t="inlineStr">
-        <is>
-          <t>（1）操作列「停用/恢复」走二次确认
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>0824周一更新
+（1）操作列「停用/恢复」走二次确认
 （2）停用父机构只暂停父机构自身，不自动停用子机构，避免误伤独立经营主体；确认框列出仍在运营的子机构，如需停用须逐家确认并分别留痕
 （3）停用（danger）：「停用「X」后该机构后台与前台均提示『机构服务已暂停』，C 端用户无法访问，可随时恢复」
-（4）恢复：「访问将立即解封」</t>
+（4）恢复：「访问将立即解封」；「0824 补充」恢复弹窗同时说明「已停用期间解除的会员自动续费签约不会自动恢复，用户须在会员中心重新开通」
+（5）「0824 新增」机构停用的 C 端会员计费处理定版（详见 PRD 4.4.5 ④-3）。① 停用生效当天：对该机构全部开通自动续费的会员批量解除微信代扣签约、停止后续扣款，并发送一条合并停服短信（仅发自动续费会员——短信的不可替代价值是阻止预期外的资金变动，只有他们有资金风险；单月会员/永享用户由 C 端停用拦截态在下次打开时告知，不发短信）。之后无任何后续通知。② 会员时长不冻结：到期→宽限→过期走既有四态，零新增状态机（停用是低频终局事件，用无界的状态机复杂度对冲有界的小额敞口不成立）。③ 恢复机构零动作：不自动恢复签约、不发通知——解约后不存在「扣款悄悄恢复」的可能，无资金风险即无通知义务；用户续开自动续费须在会员中心重新签约（新的代扣授权）。④ 停用确认弹窗显性化告知操作者全部代价，文案定版为有序编号 + 重点加粗 + 琥珀警示引用块（淡底 + 左色条），弹窗加宽 30%（400→520px）、文案精简为两条：① 机构停用后，将立即解除 N 位自动续费会员的代扣签约，不再扣款，并向其发送停服通知短信；② 有效会员与永享用户共 M 位，剩余权益建议按未消费天数退款——需机构方操作，平台不自动退款（文案结构见 suspensionBillingImpact，人数为演示推导值）。⑤ 短信模版（签名固定【科技文献出版社】，机构名走变量；0824-2 措辞定版「因机构服务调整」——向用户如实归因到机构侧、但用中性的「服务调整」表述，不引发「平台与机构出了什么问题」的联想）——标准版：「【科技文献出版社】因机构服务调整，您在${机构名}的AI问书服务已暂停，暂时无法使用。您的会员自动续费已同步取消，不会再扣款。如有其他问题，请登录AI问书进入【我的-联系客服】。」纠正版（已发出扣费前 5 天提醒、扣款日未到，须撤回扣款承诺）：「【科技文献出版社】因机构服务调整，您在${机构名}的AI问书服务已暂停，暂时无法使用。原定${扣费日}的会员自动续费已取消，不会扣款。如有其他问题，请登录AI问书进入【我的-联系客服】。」⑥ 合法性口径：解约＝商户放弃自身收款授权（无需对方同意），微信提供商户侧解约接口属平台认可行为；配合合体协议「机构服务变动」条款（有约定）+ 停服短信（有告知）+ 既有权益可退款（权益不受损）</t>
         </is>
       </c>
     </row>

--- a/docs/feature-list.xlsx
+++ b/docs/feature-list.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E141"/>
+  <dimension ref="A1:E142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1005,23 +1005,25 @@
           <t>AI 会话</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>答案溯源抽屉</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>（1）答案下「参考 N 篇知识」入口，点击从右侧抽屉拉出溯源列表，仅按相关度从高到低排序、不显数值
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>0918周五更新
+（1）答案下「参考 N 篇知识」入口，点击从右侧抽屉拉出溯源列表，仅按相关度从高到低排序、不显数值
 （2）分两块、中间浅灰横线分隔：上块知识 KP（KP 封面 + KP 名 + 文件名 + 章节页码；同 KP 多命中文件归并最多 2 个、其余「…等 N 个文件」），下块互联网检索（站点用小圆形图标）
 （3）字段过长尾部省略号截断
-（4）条目点击：book 类型跳该 KP 纸书购买链接，链接为空提示「暂不可查看详情」；web 类型打开来源网页
-（5）溯源条目引用的 KP 已下架 / 已删除时，条目名后加灰标「已下架 / 已失效」，点击不跳转、提示相应失效文案</t>
+（4）条目点击：book 类型跳该 KP 第三方跳转链接，链接为空提示「暂不可查看详情」；web 类型打开来源网页
+（5）溯源条目引用的 KP 已下架 / 已删除时，条目名后加灰标「已下架 / 已失效」，点击不跳转、提示相应失效文案
+（6）「0918 修订」KP 基础信息字段「纸书购买链接」改名「第三方跳转链接」（不限纸书购买页，出版社官网 / 电商店铺等均可），溯源跳转规则不变</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1050,7 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>（1）所有「跳出 AI 问书」的链接（web 互联网来源 + 知识 KP 的纸书/运营填写链接）均先弹过渡提示
+          <t>（1）所有「跳出 AI 问书」的链接（web 互联网来源 + 知识 KP 的第三方跳转链接）均先弹过渡提示
 （2）样式为屏幕中上方黑底白字倒计时条：左侧 3·2·1 倒计时 + 「即将跳转到外部」+ 右侧「取消跳转」
 （3）倒计时结束打开来源网页；点「取消跳转」中止；触发时不关闭右侧溯源抽屉，提示叠在当前页之上
 （4）倒计时浮层不展示具体 URL（仅文案提示）</t>
@@ -2022,19 +2024,20 @@
           <t>知识产品 KP</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>KP 详情 · 基础信息</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>（1）详情头：返回 + KP 名（与列表同源）+ 来源标签 + 状态标签（草稿/已发布/已下架，两后台命名统一）+ 右侧状态操作按钮——0717 #2.1/#2.2：草稿→「发布」、已发布→「下架」、已下架→「重新发布」；删除对草稿/已发布/已下架均可用；操作真实生效（原型内真实改状态，非仅提示）。0717 二批 #2/#4：来源标签统一「自建 / 共享」（详情不再用「共享导入」，与列表一致）；实时同步导入的详情头不再显示「实时同步 · 只读」附加标（顶部只读 banner 已说明）
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>0918周五更新
+（1）详情头：返回 + KP 名（与列表同源）+ 来源标签 + 状态标签（草稿/已发布/已下架，两后台命名统一）+ 右侧状态操作按钮——0717 #2.1/#2.2：草稿→「发布」、已发布→「下架」、已下架→「重新发布」；删除对草稿/已发布/已下架均可用；操作真实生效（原型内真实改状态，非仅提示）。0717 二批 #2/#4：来源标签统一「自建 / 共享」（详情不再用「共享导入」，与列表一致）；实时同步导入的详情头不再显示「实时同步 · 只读」附加标（顶部只读 banner 已说明）
 （2）「发布」同样走二次确认——弹窗说明「发布后前台立即可见：支持检索、购买、扫码与链接访问；发布需至少一份已向量化完成的知识内容」，确认后状态真实置为已发布并 toast「已发布」
 （3）0717 #1.4：下架＝运营临时禁止访问（处理完问题可随时重新发布）——停止检索、新购买、新扫码与链接访问；C 端「我的纸书」「我的永享」等入口统一显「已下架」、点击提示联系客服、暂不可进入会话/预览；已购权益不清除，重新发布后自动恢复访问
 （4）0717 #1.8：下架确认弹窗结构化——无序列表明示前台影响（我的纸书/我的永享显「已下架」、暂不可进入；已购权益保留、重新发布自动恢复）+ 琥珀提示块说明下架适用于「临时禁止访问、处理完再上架」的运营场景
@@ -2042,11 +2045,12 @@
 （6）删除确认弹窗按有无业务关系区分内容：无关系→简明确认（明示逻辑删除口径：三端不再展示、数据库保留数据、前台提示「已失效」）；有关系→无序列表列出影响要点 + 淡红警示引用块统计「N 位已购永享用户」与「M 位纸书扫码解锁用户」，明确告知对 C 端「我的永享 / 我的纸书 / 新会话与扫码入口 / 历史 AI 会话 / 订单记录」的影响
 （7）0717【KP 状态 × 前台影响矩阵】（终版）——▸ 新 AI 会话（KP 前台地址进入）：已发布＝正常进入；已下架＝提示「已下架，若有问题请联系客服」3 秒 → 跳转规则①；已删除＝提示「已失效，若有问题请联系客服」3 秒 → 跳转规则①。▸ 知识 KP 二维码扫码（含首扫权益绑定核销）：规则与「新 AI 会话（前台地址进入）」完全相同——已下架 / 已删除提示相应文案 3 秒后跳转至当前机构最新已发布的 KP（跳转规则①）（注意用词：兑换码的权益是会员，与 KP 绑定的是「知识 KP 二维码」）。▸ 我的纸书：已下架＝标「已下架」（已解锁则并列保留「已解锁」标）、点击拦截提示联系客服；已删除＝标「已失效」拦截。▸ 我的永享：同我的纸书——已下架拦截（权益保留、重新上架自动恢复）、已删除标「已失效」拦截。▸ 草稿：新会话 / 二维码扫码均按「已失效」处理。▸ 历史会话 / 内容溯源：已下架 / 已删除分别灰标「已下架 / 已失效」。跳转规则①：目标＝本 KP 同机构下最新创建且已发布的 KP 会话；未登录先进登录界面（仅当存在目标）；机构无满足条件 KP 则不跳转、也不进登录界面。订单记录一律保留可查
 （8）左侧 9:16 封面区（上传/重新上传/删除，上传走「裁剪封面 9:16」弹窗、裁剪框可拖拽）
-（9）右侧表单：KP 名称（必填）、简介、纸书购买链接（填写后用户查看溯源时可跳转）、关联 Agent（必填，下拉）
-（10）前台访问地址（5.3）：只读链接 + 复制按钮，随当前环境（本地/线上）自动生成；说明移到字段名旁问号 icon 的 hover 面板、用无序列表两行不换行展示（① C 端用户访问本机构该 KP 的前台地址 ② 随当前环境自动生成），字段下方不再常驻长文案
-（11）前台访问地址由机构域名前缀与当前环境根域名动态生成：输入 test 时为 test-aba.{当前环境根域名}，KP 链接追加 /kp/{kpId}，机构后台追加 /admin/
-（12）底部「保存」→ toast「已保存」
-（13）「0718 修订」详情头来源标签与列表统一为三态——自建 / 分享导入·实时 / 分享导入·快照，统一灰色（原自建靛蓝取消）；旧「共享」二分法废弃</t>
+（9）右侧表单：KP 名称（必填）、简介、第三方跳转链接（填写后用户查看溯源时可跳转）、关联 Agent（必填，下拉）
+（10）「0918 修订」字段「纸书购买链接」改名「第三方跳转链接」——链接不限纸书购买页（出版社官网 / 电商店铺等均可），输入框提示改为「如纸书购买页、官网等，用户查看溯源时可跳转」；选填、跳转规则不变，平台后台全域 KP 详情同步
+（11）前台访问地址（5.3）：只读链接 + 复制按钮，随当前环境（本地/线上）自动生成；说明移到字段名旁问号 icon 的 hover 面板、用无序列表两行不换行展示（① C 端用户访问本机构该 KP 的前台地址 ② 随当前环境自动生成），字段下方不再常驻长文案
+（12）前台访问地址由机构域名前缀与当前环境根域名动态生成：输入 test 时为 test-aba.{当前环境根域名}，KP 链接追加 /kp/{kpId}，机构后台追加 /admin/
+（13）底部「保存」→ toast「已保存」
+（14）「0718 修订」详情头来源标签与列表统一为三态——自建 / 分享导入·实时 / 分享导入·快照，统一灰色（原自建靛蓝取消）；旧「共享」二分法废弃</t>
         </is>
       </c>
     </row>
@@ -3769,21 +3773,23 @@
           <t>机构账户</t>
         </is>
       </c>
-      <c r="C105" s="3" t="inlineStr">
+      <c r="C105" s="4" t="inlineStr">
         <is>
           <t>机构账户列表</t>
         </is>
       </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E105" s="6" t="inlineStr">
-        <is>
-          <t>（1）表格列：账户 ID、账户名、姓名、机构、上级机构、角色（管理员/运营/只读）、状态（正常/停用）、操作（操作列固定右侧）——「所属机构」列名统一为「机构」
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>0918周五更新
+（1）表格列：账户 ID、账户名、姓名、机构、上级机构、角色（管理员/运营/只读）、状态（正常/停用）、操作（操作列固定右侧）——「所属机构」列名统一为「机构」
 （2）按 账户名/姓名 搜索；筛选 机构、上级机构、角色、状态
-（3）筛选行右侧新增「导出」：生成「AI问书_全域机构账户数据导出.xlsx」，沿用全部搜索与筛选；头部注明导出时间与筛选条件</t>
+（3）筛选行右侧新增「导出」：生成「AI问书_全域机构账户数据导出.xlsx」，沿用全部搜索与筛选；头部注明导出时间与筛选条件
+（4）「0918 修订」导出新增「密码」列（紧跟账户名），明文导出当前登录密码（重置密码后导出的即为新密码）；导出 toast 提示「文件含明文密码，请妥善保管」。技术前提：密码须可逆加密存储（不能只存哈希），否则无法导出原文</t>
         </is>
       </c>
     </row>
@@ -3798,17 +3804,48 @@
           <t>机构账户</t>
         </is>
       </c>
-      <c r="C106" s="3" t="inlineStr">
+      <c r="C106" s="4" t="inlineStr">
         <is>
           <t>机构账户列表</t>
         </is>
       </c>
-      <c r="D106" s="3" t="inlineStr">
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>批量导入</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>0918周五新增
+（1）「0918 新增」页头「新建账户」左侧新增「批量导入」按钮，弹窗四步：① 下载导入模板（AI问书_全域机构账户导入模板.xlsx，列＝账户名 / 密码 / 姓名 / 机构 / 角色 / 联系电话，新建必填列表头赭色标记，机构与角色列带下拉）→ ② 上传 .xlsx（点击或拖拽；「导出」的文件也可直接修改后上传，按表头名取列、多余列忽略）→ ③ 解析校验预览：新建 N / 更新 N / 错误 N 三数卡 + 错误明细（行号 + 账户名 + 原因，可下载错误明细）→ ④ 确认导入后展示结果，可「下载导入结果」（含新建账户的明文密码）
+（2）「0918 新增」匹配规则：按「账户名」匹配（不区分大小写）——不存在则自动新建（状态正常），已存在则更新；更新时留空的单元格不修改，填写密码即重置为该密码；新建时账户名 / 姓名 / 机构 / 角色必填，密码留空由系统生成。导入不改账户状态（停用 / 恢复仍走列表二次确认）
+（3）「0918 新增」条数上限：单次最多 500 条，超出整份拒绝（不截断，避免「以为全导了其实只导了一部分」），提示「文件共 N 条，超过单次上限 500 条，请拆分为多个文件后分批导入」
+（4）「0918 新增」逐行校验：账户名 3–32 位（字母 / 数字 / _ - . @）/ 文件内账户名重复（报「与第 N 行重复」）/ 机构须存在 / 角色须为管理员·运营·只读 / 联系电话须 11 位手机号 / 密码须符合密码规则（8–16 位，同时含字母和数字，不含空格）；错误行跳过、其余照常导入（按钮文案「跳过错误行，导入 N 条」），全部有误时导入按钮置灰</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>平台超管后台 PC</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>机构账户</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>机构账户列表</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
         <is>
           <t>新建 / 编辑账户</t>
         </is>
       </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="E107" s="6" t="inlineStr">
         <is>
           <t>（1）新建/编辑共用弹窗：账户名称、姓名、机构、角色、联系手机号；账户名称创建后不可修改——编辑态该字段置灰并注「账户名称创建后不可修改」；平台后台列表、详情与弹窗均完整展示手机号，不脱敏
 （2）校验账户名+姓名非空（toast「请填写账户名称与姓名」）
@@ -3817,35 +3854,6 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>平台超管后台 PC</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>机构账户</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="inlineStr">
-        <is>
-          <t>机构账户列表</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>重置密码 / 停用恢复</t>
-        </is>
-      </c>
-      <c r="E107" s="6" t="inlineStr">
-        <is>
-          <t>（1）重置密码 → 弹凭证弹窗（账号 + 系统生成密码）+ toast「已重置密码」
-（2）停用/恢复二次确认：停用（danger）「停用账户「X」后将无法登录机构后台，提示『账户服务已暂停』，可随时恢复」
-（3）凭证弹窗：明文展示 账号/密码/姓名/机构/角色 +「一键复制」（toast「已复制账户凭证」）+ 提示「密码仅此一次明文展示」</t>
-        </is>
-      </c>
-    </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
@@ -3854,20 +3862,51 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
+          <t>机构账户</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>机构账户列表</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>重置密码 / 停用恢复</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>0918周五更新
+（1）重置密码 → 弹凭证弹窗（账号 + 系统生成密码）+ toast「已重置密码」
+（2）停用/恢复二次确认：停用（danger）「停用账户「X」后将无法登录机构后台，提示『账户服务已暂停』，可随时恢复」
+（3）凭证弹窗：明文展示 账号/密码/姓名/机构/角色 +「一键复制」（toast「已复制账户凭证」）+ 提示「密码仅此一次明文展示」
+（4）「0918 修订」机构账户凭证弹窗提示改为「请妥善保存并发送给账户使用人；机构账户密码也可通过列表「导出」获取」（导出已含明文密码，「仅此一次」不再成立）；平台账户凭证弹窗提示不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>平台超管后台 PC</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
           <t>订阅订单（全域 B 端）</t>
         </is>
       </c>
-      <c r="C108" s="3" t="inlineStr">
+      <c r="C109" s="3" t="inlineStr">
         <is>
           <t>全域订阅订单</t>
         </is>
       </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
         <is>
           <t>（1）定位：B 端订阅（机构→平台），与 C 端「全域订单」两套体系；列表只展示「订阅」，加油包不入表
 （2）顶部 5 KPI（带 InfoDot）：订阅总数、生效、未生效、加油包、90 天内到期
@@ -3876,33 +3915,6 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>平台超管后台 PC</t>
-        </is>
-      </c>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>订阅订单（全域 B 端）</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="inlineStr">
-        <is>
-          <t>全域订阅订单</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>加油包抽屉</t>
-        </is>
-      </c>
-      <c r="E109" s="6" t="inlineStr">
-        <is>
-          <t>（1）同机构详情加油包抽屉：即时生效·额度累加·有效期跟随订阅；至少一项额度 &gt;0；列出加油包记录</t>
-        </is>
-      </c>
-    </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
@@ -3911,20 +3923,47 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
+          <t>订阅订单（全域 B 端）</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>全域订阅订单</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>加油包抽屉</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>（1）同机构详情加油包抽屉：即时生效·额度累加·有效期跟随订阅；至少一项额度 &gt;0；列出加油包记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>平台超管后台 PC</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
           <t>全域知识产品 KP</t>
         </is>
       </c>
-      <c r="C110" s="3" t="inlineStr">
+      <c r="C111" s="3" t="inlineStr">
         <is>
           <t>全域 KP 列表</t>
         </is>
       </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E110" s="6" t="inlineStr">
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
         <is>
           <t>（1）卡片网格（复用机构后台 KP 卡视觉），平台只读监管
 （2）每卡：封面 + KP 名 +「机构 · {orgName}」（平台视角必显）+ 状态标签（已发布/草稿/已下架）+ 永享标
@@ -3936,36 +3975,6 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>平台超管后台 PC</t>
-        </is>
-      </c>
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t>全域知识产品 KP</t>
-        </is>
-      </c>
-      <c r="C111" s="3" t="inlineStr">
-        <is>
-          <t>全域 KP 详情（5 Tab，与机构后台同构）</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>基础信息</t>
-        </is>
-      </c>
-      <c r="E111" s="6" t="inlineStr">
-        <is>
-          <t>（1）与机构后台 KP 详情·基础信息一致：封面（裁剪）+ KP 名称（必填）/简介/纸书购买链接/关联 Agent（必填）+ 保存
-（2）前台访问地址：只读展示 + 「复制链接」一键复制 C 端前台访问地址（随当前环境自动生成，携带机构 + KP），同机构后台
-（3）头部状态操作与机构后台一致：草稿→「发布」、已发布→「下架」、已下架→「重新发布」+「删除」（逻辑删除，删除后回全域 KP 列表）
-（4）「0718 修订」详情头来源标签与机构后台统一三态灰色；平台超管查看「分享导入·实时」的 KP 时不套用接收方只读——保留发布/下架/删除等监管操作，仅以来源标签提示该 KP 为实时导入</t>
-        </is>
-      </c>
-    </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
@@ -3977,50 +3986,55 @@
           <t>全域知识产品 KP</t>
         </is>
       </c>
-      <c r="C112" s="3" t="inlineStr">
+      <c r="C112" s="4" t="inlineStr">
         <is>
           <t>全域 KP 详情（5 Tab，与机构后台同构）</t>
         </is>
       </c>
-      <c r="D112" s="3" t="inlineStr">
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>基础信息</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>0918周五更新
+（1）与机构后台 KP 详情·基础信息一致：封面（裁剪）+ KP 名称（必填）/简介/第三方跳转链接/关联 Agent（必填）+ 保存
+（2）「0918 修订」字段「纸书购买链接」改名「第三方跳转链接」，与机构后台同源组件同步生效
+（3）前台访问地址：只读展示 + 「复制链接」一键复制 C 端前台访问地址（随当前环境自动生成，携带机构 + KP），同机构后台
+（4）头部状态操作与机构后台一致：草稿→「发布」、已发布→「下架」、已下架→「重新发布」+「删除」（逻辑删除，删除后回全域 KP 列表）
+（5）「0718 修订」详情头来源标签与机构后台统一三态灰色；平台超管查看「分享导入·实时」的 KP 时不套用接收方只读——保留发布/下架/删除等监管操作，仅以来源标签提示该 KP 为实时导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>平台超管后台 PC</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>全域知识产品 KP</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>全域 KP 详情（5 Tab，与机构后台同构）</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
         <is>
           <t>知识库</t>
         </is>
       </c>
-      <c r="E112" s="6" t="inlineStr">
+      <c r="E113" s="6" t="inlineStr">
         <is>
           <t>（1）与机构后台一致：上传知识文件（左右布局、向量化状态机）、文件上下架/重试/删除、类型筛选、检索状态
 （2）与机构后台一致：原『永享』Tab 取消、并入知识库——图/音/视可设永享价 + 永享/非永享标签 + 预览；设价弹窗含独立权益说明块</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>平台超管后台 PC</t>
-        </is>
-      </c>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>全域知识产品 KP</t>
-        </is>
-      </c>
-      <c r="C113" s="3" t="inlineStr">
-        <is>
-          <t>全域 KP 详情（5 Tab，与机构后台同构）</t>
-        </is>
-      </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>定价与权益</t>
-        </is>
-      </c>
-      <c r="E113" s="6" t="inlineStr">
-        <is>
-          <t>（1）与机构后台一致：免费/会员 二选一互斥（0717 #5 切换前二次确认）；永享与会员两套独立权益（设了永享价的资源会员也需单独购买）</t>
-        </is>
-      </c>
-    </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
@@ -4039,12 +4053,12 @@
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>二维码</t>
+          <t>定价与权益</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>（1）与机构后台一致：二维码包列表 + 新建包 + 明细抽屉 + 下载 zip</t>
+          <t>（1）与机构后台一致：免费/会员 二选一互斥（0717 #5 切换前二次确认）；永享与会员两套独立权益（设了永享价的资源会员也需单独购买）</t>
         </is>
       </c>
     </row>
@@ -4066,12 +4080,12 @@
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>分享</t>
+          <t>二维码</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>（1）与机构后台一致：分享列表 + 新建分享 + 取消分享</t>
+          <t>（1）与机构后台一致：二维码包列表 + 新建包 + 明细抽屉 + 下载 zip</t>
         </is>
       </c>
     </row>
@@ -4083,20 +4097,47 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
+          <t>全域知识产品 KP</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>全域 KP 详情（5 Tab，与机构后台同构）</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>分享</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>（1）与机构后台一致：分享列表 + 新建分享 + 取消分享</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>平台超管后台 PC</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
           <t>全域 Agent 人设</t>
         </is>
       </c>
-      <c r="C116" s="3" t="inlineStr">
+      <c r="C117" s="3" t="inlineStr">
         <is>
           <t>全域 Agent 列表</t>
         </is>
       </c>
-      <c r="D116" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E116" s="6" t="inlineStr">
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
         <is>
           <t>（1）卡片网格：渐变封面 + Agent 名 +「机构 · {org}」+ 类型标签 +「关联 KP N 个」+ 音色（已设/默认）
 （2）按 Agent 名称搜索 + 机构筛选
@@ -4104,28 +4145,28 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B117" s="3" t="inlineStr">
+      <c r="B118" s="3" t="inlineStr">
         <is>
           <t>全域 Agent 人设</t>
         </is>
       </c>
-      <c r="C117" s="4" t="inlineStr">
+      <c r="C118" s="4" t="inlineStr">
         <is>
           <t>全域 Agent 详情（人设风格平台可编辑）</t>
         </is>
       </c>
-      <c r="D117" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E117" s="5" t="inlineStr">
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
         <is>
           <t>0812周三更新
 （1）表单同机构后台 Agent 详情：头像（必填，圆形裁剪）、名称（必填）、类型（只读不可改）、TTS 参考音（必填）、TTS 参考音文本（必填）
@@ -4136,28 +4177,28 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B118" s="3" t="inlineStr">
+      <c r="B119" s="3" t="inlineStr">
         <is>
           <t>全域用户</t>
         </is>
       </c>
-      <c r="C118" s="4" t="inlineStr">
+      <c r="C119" s="4" t="inlineStr">
         <is>
           <t>全域用户列表</t>
         </is>
       </c>
-      <c r="D118" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E118" s="5" t="inlineStr">
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
         <is>
           <t>0807周五更新
 （1）表格列：用户昵称、微信号、手机号、机构、会员状态、已购永享、累计 GMV、最新登录时间、注册时间、操作（详情）——「归属机构」列名统一为「机构」；「注册时间」列支持升 / 降序排序
@@ -4168,28 +4209,28 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B119" s="3" t="inlineStr">
+      <c r="B120" s="3" t="inlineStr">
         <is>
           <t>全域用户</t>
         </is>
       </c>
-      <c r="C119" s="4" t="inlineStr">
+      <c r="C120" s="4" t="inlineStr">
         <is>
           <t>全域用户详情</t>
         </is>
       </c>
-      <c r="D119" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="inlineStr">
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
         <is>
           <t>0807周五更新
 （1）头部卡：头像 + 昵称 + 会员状态标签（四态）；副行「机构 · 手机号 · 微信号」；活跃度（近 30 天提问 · 累计 GMV · 最近活跃）
@@ -4199,28 +4240,28 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B120" s="3" t="inlineStr">
+      <c r="B121" s="3" t="inlineStr">
         <is>
           <t>全域订单</t>
         </is>
       </c>
-      <c r="C120" s="3" t="inlineStr">
+      <c r="C121" s="3" t="inlineStr">
         <is>
           <t>全域订单列表</t>
         </is>
       </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
         <is>
           <t>（1）C 端订单（终端用户→机构），复用订单字段，多「机构」列与筛选——「归属机构」列名统一为「机构」
 （2）表格列：订单号、机构、类型、关联知识产品、金额、支付方式、订单状态、退款状态、用户、下单时间、付款时间、兑换时间、操作（详情）
@@ -4230,28 +4271,28 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B121" s="3" t="inlineStr">
+      <c r="B122" s="3" t="inlineStr">
         <is>
           <t>全域订单</t>
         </is>
       </c>
-      <c r="C121" s="3" t="inlineStr">
+      <c r="C122" s="3" t="inlineStr">
         <is>
           <t>全域订单详情</t>
         </is>
       </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E121" s="6" t="inlineStr">
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
         <is>
           <t>（1）结构同机构后台订单详情，额外显「机构」字段（原「归属机构」统一更名）
 （2）兑换码/会员/永享三类差异化；有退款记录时显退款信息卡 + 退款时间线
@@ -4259,28 +4300,28 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B122" s="3" t="inlineStr">
+      <c r="B123" s="3" t="inlineStr">
         <is>
           <t>全域答案反馈</t>
         </is>
       </c>
-      <c r="C122" s="4" t="inlineStr">
+      <c r="C123" s="4" t="inlineStr">
         <is>
           <t>全域答案反馈工作台</t>
         </is>
       </c>
-      <c r="D122" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E122" s="5" t="inlineStr">
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
         <is>
           <t>0807周五更新
 （1）副标题「全平台各机构 C 端答案点踩/反馈汇总，便于平台监管与质量分析」
@@ -4292,28 +4333,28 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B123" s="3" t="inlineStr">
+      <c r="B124" s="3" t="inlineStr">
         <is>
           <t>全域模型用量</t>
         </is>
       </c>
-      <c r="C123" s="3" t="inlineStr">
+      <c r="C124" s="3" t="inlineStr">
         <is>
           <t>全域模型用量</t>
         </is>
       </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
         <is>
           <t>（1）页头机构筛选覆盖全部机构，父机构带「父机构」标签；选中父机构＝自动汇总该父机构自身及其全部子机构数据
 （2）右侧「导出」：生成「AI问书_全域模型用量数据导出.xlsx」，沿用机构范围与时间区间，实时/区间口径分别标注统计时间；头部注明导出时间与筛选条件
@@ -4324,28 +4365,28 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B124" s="3" t="inlineStr">
+      <c r="B125" s="3" t="inlineStr">
         <is>
           <t>平台账户</t>
         </is>
       </c>
-      <c r="C124" s="3" t="inlineStr">
+      <c r="C125" s="3" t="inlineStr">
         <is>
           <t>平台账户列表</t>
         </is>
       </c>
-      <c r="D124" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E125" s="6" t="inlineStr">
         <is>
           <t>（1）副标题强调与机构账户区分：平台方人员、平台级角色、无所属机构
 （2）表格列：账户名称、姓名、角色（平台超级管理员/平台运营/平台财务）、完整手机号、状态（启用/停用）、创建时间、操作；手机号不脱敏
@@ -4354,28 +4395,28 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B125" s="3" t="inlineStr">
+      <c r="B126" s="3" t="inlineStr">
         <is>
           <t>平台账户</t>
         </is>
       </c>
-      <c r="C125" s="3" t="inlineStr">
+      <c r="C126" s="3" t="inlineStr">
         <is>
           <t>平台账户列表</t>
         </is>
       </c>
-      <c r="D125" s="3" t="inlineStr">
+      <c r="D126" s="3" t="inlineStr">
         <is>
           <t>新建 / 重置密码 / 启停</t>
         </is>
       </c>
-      <c r="E125" s="6" t="inlineStr">
+      <c r="E126" s="6" t="inlineStr">
         <is>
           <t>（1）新建弹窗：账户名称（必填）、姓名（必填）、角色（必填，平台三角色）、联系方式（选填）；说明「平台账户无所属机构，仅用平台级角色 / 初始密码系统生成，创建后弹窗展示并支持复制」
 （2）校验账户名+姓名非空；新建成功弹凭证弹窗（机构标「平台（无所属机构）」）
@@ -4383,28 +4424,28 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B126" s="3" t="inlineStr">
+      <c r="B127" s="3" t="inlineStr">
         <is>
           <t>角色权限</t>
         </is>
       </c>
-      <c r="C126" s="4" t="inlineStr">
+      <c r="C127" s="4" t="inlineStr">
         <is>
           <t>角色权限（机构/平台双类型 · 三态）</t>
         </is>
       </c>
-      <c r="D126" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E126" s="5" t="inlineStr">
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
         <is>
           <t>0807周五更新
 （1）副标题「按角色类型分别管理机构角色与平台角色（权限点不同）；机构账户选机构角色、平台账户选平台角色」
@@ -4418,56 +4459,56 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B127" s="3" t="inlineStr">
+      <c r="B128" s="3" t="inlineStr">
         <is>
           <t>角色权限</t>
         </is>
       </c>
-      <c r="C127" s="3" t="inlineStr">
+      <c r="C128" s="3" t="inlineStr">
         <is>
           <t>角色权限（机构/平台双类型 · 三态）</t>
         </is>
       </c>
-      <c r="D127" s="3" t="inlineStr">
+      <c r="D128" s="3" t="inlineStr">
         <is>
           <t>新建角色</t>
         </is>
       </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="E128" s="6" t="inlineStr">
         <is>
           <t>（1）弹窗加宽，使角色类型一行完整展示不换行；角色类型继承当前“机构角色/平台角色”Tab并以置灰锁定显示，不可切换；删除解释文案「由创建入口页签决定，不可切换」（锁定态样式已自说明）；仅填写角色名称与备注
 （2）校验名称非空 + 同类型不重名；创建后入对应类型列表、空权限、自动切换选中 → toast「已创建角色，请在右侧逐项设置权限」</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B128" s="3" t="inlineStr">
+      <c r="B129" s="3" t="inlineStr">
         <is>
           <t>默认 LLM</t>
         </is>
       </c>
-      <c r="C128" s="3" t="inlineStr">
+      <c r="C129" s="3" t="inlineStr">
         <is>
           <t>默认 LLM 模型配置</t>
         </is>
       </c>
-      <c r="D128" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E128" s="6" t="inlineStr">
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="inlineStr">
         <is>
           <t>（1）副标题「仅『已上架』的模型可被设为所有机构底层的默认基模」
 （2）表格：模型名称、厂商、版本号、状态（已上架/未上架 + 默认标）、操作（编辑/上架·下架/设为默认）
@@ -4476,33 +4517,6 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>平台超管后台 PC</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>默认 LLM</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="inlineStr">
-        <is>
-          <t>默认 LLM 模型配置</t>
-        </is>
-      </c>
-      <c r="D129" s="3" t="inlineStr">
-        <is>
-          <t>新建 / 编辑模型</t>
-        </is>
-      </c>
-      <c r="E129" s="6" t="inlineStr">
-        <is>
-          <t>（1）弹窗：模型名称（必填，唯一校验，重名实时红字 + toast「模型名称已存在」）、厂商（下拉 通义/DeepSeek/智谱/百川）、版本号（必填）、状态（编辑时只读，注「上下架请在列表操作列进行」）</t>
-        </is>
-      </c>
-    </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
@@ -4511,53 +4525,53 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
+          <t>默认 LLM</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>默认 LLM 模型配置</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>新建 / 编辑模型</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>（1）弹窗：模型名称（必填，唯一校验，重名实时红字 + toast「模型名称已存在」）、厂商（下拉 通义/DeepSeek/智谱/百川）、版本号（必填）、状态（编辑时只读，注「上下架请在列表操作列进行」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>平台超管后台 PC</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
           <t>个人中心</t>
         </is>
       </c>
-      <c r="C130" s="3" t="inlineStr">
+      <c r="C131" s="3" t="inlineStr">
         <is>
           <t>个人中心</t>
         </is>
       </c>
-      <c r="D130" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E130" s="6" t="inlineStr">
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
         <is>
           <t>（1）账户信息只读：账户名称、姓名、角色、完整手机号、账户状态；两后台个人中心手机号均不脱敏，平台账户不显示所属机构/上级机构
 （2）平台超管不显示「账户信息由平台统一管理…」灰字提示</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>平台超管后台 PC</t>
-        </is>
-      </c>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>个人中心</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="inlineStr">
-        <is>
-          <t>个人中心</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>更换头像（裁剪）</t>
-        </is>
-      </c>
-      <c r="E131" s="6" t="inlineStr">
-        <is>
-          <t>（1）相册选图 → 圆形裁剪（拖拽定位 + 缩放滑块）→ canvas 输出 256px 头像 → toast「头像已更新」</t>
-        </is>
-      </c>
-    </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
@@ -4576,12 +4590,12 @@
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>修改登录密码</t>
+          <t>更换头像（裁剪）</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>（1）弹窗：旧密码 + 新密码 + 确认新密码；校验 旧密码非空/新密码 8~16 位含字母+数字/两次一致 → toast「登录密码已修改」</t>
+          <t>（1）相册选图 → 圆形裁剪（拖拽定位 + 缩放滑块）→ canvas 输出 256px 头像 → toast「头像已更新」</t>
         </is>
       </c>
     </row>
@@ -4593,109 +4607,109 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
+          <t>个人中心</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>个人中心</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>修改登录密码</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>（1）弹窗：旧密码 + 新密码 + 确认新密码；校验 旧密码非空/新密码 8~16 位含字母+数字/两次一致 → toast「登录密码已修改」</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>平台超管后台 PC</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
           <t>评审工具</t>
         </is>
       </c>
-      <c r="C133" s="3" t="inlineStr">
+      <c r="C134" s="3" t="inlineStr">
         <is>
           <t>原型清单 / 微信对接清单下载</t>
         </is>
       </c>
-      <c r="D133" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E133" s="6" t="inlineStr">
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
         <is>
           <t>（1）〔评审〕原型清单：三端通用站点地图，列全站页面便于评审跳转
 （2）〔评审〕顶栏固定「新机构入驻微信对接清单」下载按钮（下载对接清单 docx）</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>三端通用（全局交互）</t>
         </is>
       </c>
-      <c r="B134" s="3" t="inlineStr">
+      <c r="B135" s="3" t="inlineStr">
         <is>
           <t>通用状态规范</t>
         </is>
       </c>
-      <c r="C134" s="3" t="inlineStr">
+      <c r="C135" s="3" t="inlineStr">
         <is>
           <t>Toast 轻提示</t>
         </is>
       </c>
-      <c r="D134" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E134" s="6" t="inlineStr">
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
         <is>
           <t>（1）单条、统一位置弹出（移动端底部 / 后台顶部），默认数秒自动消失
 （2）用于操作结果反馈（已保存/已删除/已复制等），文案过长自动换行不超屏</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>三端通用（全局交互）</t>
         </is>
       </c>
-      <c r="B135" s="3" t="inlineStr">
+      <c r="B136" s="3" t="inlineStr">
         <is>
           <t>通用状态规范</t>
         </is>
       </c>
-      <c r="C135" s="3" t="inlineStr">
+      <c r="C136" s="3" t="inlineStr">
         <is>
           <t>二次确认弹窗（ConfirmDialog）</t>
         </is>
       </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
         <is>
           <t>（1）危险/不可逆操作（删除/下架/停用/退款/取消分享等）统一走二次确认
 （2）危险操作主按钮为 danger 红色，文案写清后果与是否可恢复</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>三端通用（全局交互）</t>
-        </is>
-      </c>
-      <c r="B136" s="3" t="inlineStr">
-        <is>
-          <t>通用状态规范</t>
-        </is>
-      </c>
-      <c r="C136" s="3" t="inlineStr">
-        <is>
-          <t>加载骨架屏</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E136" s="6" t="inlineStr">
-        <is>
-          <t>（1）后台列表/详情挂载先显骨架屏占位，再渲染真实数据，避免白屏跳变</t>
-        </is>
-      </c>
-    </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
@@ -4709,48 +4723,48 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
+          <t>加载骨架屏</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E137" s="6" t="inlineStr">
+        <is>
+          <t>（1）后台列表/详情挂载先显骨架屏占位，再渲染真实数据，避免白屏跳变</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>三端通用（全局交互）</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>通用状态规范</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
           <t>空态</t>
         </is>
       </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E137" s="6" t="inlineStr">
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="inlineStr">
         <is>
           <t>（1）列表/搜索/筛选无结果时显居中插画 + 标题 + 副文案（如「没有匹配的 X / 换个条件试试」）
 （2）部分空态内嵌主操作入口（如「新建 X」）</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>三端通用（全局交互）</t>
-        </is>
-      </c>
-      <c r="B138" s="3" t="inlineStr">
-        <is>
-          <t>通用状态规范</t>
-        </is>
-      </c>
-      <c r="C138" s="3" t="inlineStr">
-        <is>
-          <t>分页</t>
-        </is>
-      </c>
-      <c r="D138" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E138" s="6" t="inlineStr">
-        <is>
-          <t>（1）后台列表默认每页 10 条，超过才分页；筛选/搜索变更后回到第 1 页；分页单位随实体变化（家/个/笔/条/单等）</t>
-        </is>
-      </c>
-    </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
@@ -4764,7 +4778,7 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>操作列固定</t>
+          <t>分页</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
@@ -4774,7 +4788,7 @@
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>（1）后台表格「操作」列固定在右侧（白底+左侧分隔线+阴影），横向滚动时常驻可见</t>
+          <t>（1）后台列表默认每页 10 条，超过才分页；筛选/搜索变更后回到第 1 页；分页单位随实体变化（家/个/笔/条/单等）</t>
         </is>
       </c>
     </row>
@@ -4791,15 +4805,42 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
+          <t>操作列固定</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="inlineStr">
+        <is>
+          <t>（1）后台表格「操作」列固定在右侧（白底+左侧分隔线+阴影），横向滚动时常驻可见</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>三端通用（全局交互）</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>通用状态规范</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
           <t>数值单位规范</t>
         </is>
       </c>
-      <c r="D140" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E140" s="6" t="inlineStr">
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr">
         <is>
           <t>（1）两后台数值统一中文进制缩写：&lt;1 万千分位；1 万~1 亿 → X.X 万；≥1 亿 → X.XX 亿；Token 统一以「亿」为单位
 （2）各看板页脚附统一单位规范说明
@@ -4810,28 +4851,28 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>三端通用（全局交互）</t>
         </is>
       </c>
-      <c r="B141" s="3" t="inlineStr">
+      <c r="B142" s="3" t="inlineStr">
         <is>
           <t>通用状态规范</t>
         </is>
       </c>
-      <c r="C141" s="3" t="inlineStr">
+      <c r="C142" s="3" t="inlineStr">
         <is>
           <t>登录态有效期</t>
         </is>
       </c>
-      <c r="D141" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E141" s="6" t="inlineStr">
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="inlineStr">
         <is>
           <t>（1）移动端采用滑动7天会话：每次经过认证的有效请求刷新最后活跃时间；连续7天无有效请求后失效并返回登录页
 （2）未登录不可进入业务内容；登录失效后的原目标地址可在重新登录成功后恢复跳转，但不自动补发任何未认证输入</t>

--- a/docs/feature-list.xlsx
+++ b/docs/feature-list.xlsx
@@ -3817,10 +3817,11 @@
       <c r="E106" s="5" t="inlineStr">
         <is>
           <t>0918周五新增
-（1）「0918 新增」页头「新建账户」左侧新增「批量导入」按钮，弹窗四步：① 下载导入模板（AI问书_全域机构账户导入模板.xlsx，列＝账户名 / 密码 / 姓名 / 机构 / 角色 / 联系电话，新建必填列表头赭色标记，机构与角色列带下拉）→ ② 上传 .xlsx（点击或拖拽；「导出」的文件也可直接修改后上传，按表头名取列、多余列忽略）→ ③ 解析校验预览：新建 N / 更新 N / 错误 N 三数卡 + 错误明细（行号 + 账户名 + 原因，可下载错误明细）→ ④ 确认导入后展示结果，可「下载导入结果」（含新建账户的明文密码）
-（2）「0918 新增」匹配规则：按「账户名」匹配（不区分大小写）——不存在则自动新建（状态正常），已存在则更新；更新时留空的单元格不修改，填写密码即重置为该密码；新建时账户名 / 姓名 / 机构 / 角色必填，密码留空由系统生成。导入不改账户状态（停用 / 恢复仍走列表二次确认）
-（3）「0918 新增」条数上限：单次最多 500 条，超出整份拒绝（不截断，避免「以为全导了其实只导了一部分」），提示「文件共 N 条，超过单次上限 500 条，请拆分为多个文件后分批导入」
-（4）「0918 新增」逐行校验：账户名 3–32 位（字母 / 数字 / _ - . @）/ 文件内账户名重复（报「与第 N 行重复」）/ 机构须存在 / 角色须为管理员·运营·只读 / 联系电话须 11 位手机号 / 密码须符合密码规则（8–16 位，同时含字母和数字，不含空格）；错误行跳过、其余照常导入（按钮文案「跳过错误行，导入 N 条」），全部有误时导入按钮置灰</t>
+（1）「0918 新增」页头「新建账户」左侧新增「批量导入」按钮，弹窗四步：① 下载导入模板（AI问书_全域机构账户导入模板.xlsx，列＝账户名 / 密码 / 姓名 / 机构 / 角色 / 联系电话，新建必填列表头赭色标记，机构与角色列带下拉；表头上方填写说明按序号逐条换行）→ ② 上传 .xlsx（点击或拖拽；「导出」的文件也可直接修改后上传，按表头名取列、多余列忽略）→ ③ 导入预览：将新建 N / 将更新 N / 有误 N · 将跳过 三数卡 + 有误明细（行号 + 账户名 + 原因，可下载），按钮「重新上传」/「确认导入 N 条」（无可导入数据时置灰）→ ④ 确认后执行导入，结果弹窗告知结果
+（2）「0918 新增」匹配规则：按「账户名」匹配（区分大小写，与手动新建一致：Admin01 与 admin01 视为两个账户；手动新建账户名完全相同时提示「账户名已存在」）——不存在则自动新建（状态正常），已存在则更新；更新时留空的单元格不修改，填写密码即重置为该密码；新建时账户名 / 姓名 / 机构 / 角色必填；密码填写则按文件设置（须符合密码规则），留空由系统生成。导入不改账户状态（停用 / 恢复仍走列表二次确认）
+（3）「0918 新增」部分成功、执行后弹窗告知：有误的行跳过、其余照常导入（不因一条错误整批失败）；结果弹窗标题按情况为「导入完成 / 部分导入成功 / 导入失败」，两张数卡＝成功 N（新建 x · 更新 y）/ 失败 N · 未导入，下方失败明细逐行列「第 N 行 + 账户名 + 失败原因」（前 50 条，可「下载失败明细」），按钮「修正后重新上传」（只传失败行即可，成功行无需重复导入）/「下载导入结果」（含新建账户明文密码）/「完成」
+（4）「0918 新增」条数上限：单次最多 500 条，超出整份拒绝（不截断，避免「以为全导了其实只导了一部分」），提示「文件共 N 条，超过单次上限 500 条，请拆分为多个文件后分批导入」
+（5）「0918 新增」逐行校验：账户名 3–32 位（字母 / 数字 / _ - . @）/ 文件内账户名重复（报「与第 N 行重复」）/ 机构须存在 / 角色须为管理员·运营·只读 / 联系电话须 11 位手机号 / 密码须符合密码规则（8–16 位，同时含字母和数字，不含空格）；错误行跳过、其余照常导入，失败原因在结果弹窗逐行展示</t>
         </is>
       </c>
     </row>
